--- a/Output Data Tables/APAT Outputs/Aggregated Tables/2023/American_Aircraft_Cumulative_Statistics_2023.xlsx
+++ b/Output Data Tables/APAT Outputs/Aggregated Tables/2023/American_Aircraft_Cumulative_Statistics_2023.xlsx
@@ -13,39 +13,42 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="24" uniqueCount="24">
   <si>
     <t>Row</t>
   </si>
   <si>
-    <t>Alaska</t>
-  </si>
-  <si>
-    <t>Allegiant</t>
-  </si>
-  <si>
-    <t>American</t>
-  </si>
-  <si>
-    <t>Breeze</t>
-  </si>
-  <si>
-    <t>Delta</t>
-  </si>
-  <si>
-    <t>Frontier</t>
-  </si>
-  <si>
-    <t>JetBlue</t>
-  </si>
-  <si>
-    <t>Spirit</t>
-  </si>
-  <si>
-    <t>United</t>
-  </si>
-  <si>
-    <t>All Airlines</t>
+    <t>A319</t>
+  </si>
+  <si>
+    <t>A320</t>
+  </si>
+  <si>
+    <t>A321</t>
+  </si>
+  <si>
+    <t>A321NEO</t>
+  </si>
+  <si>
+    <t>B737-800</t>
+  </si>
+  <si>
+    <t>B737-8</t>
+  </si>
+  <si>
+    <t>B787-8</t>
+  </si>
+  <si>
+    <t>B787-9</t>
+  </si>
+  <si>
+    <t>B777-200</t>
+  </si>
+  <si>
+    <t>B777-300</t>
+  </si>
+  <si>
+    <t>All Aircraft</t>
   </si>
   <si>
     <t>RPMs</t>
@@ -127,10 +130,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" customWidth="true"/>
+    <col min="1" max="1" width="9.28515625" customWidth="true"/>
     <col min="2" max="2" width="15.85546875" customWidth="true"/>
     <col min="3" max="3" width="15.85546875" customWidth="true"/>
     <col min="4" max="4" width="13.140625" customWidth="true"/>
@@ -150,40 +153,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="0" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" s="0" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" s="0" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K1" s="0" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L1" s="0" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M1" s="0" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2">
@@ -191,40 +194,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>36853093</v>
+        <v>14590883469</v>
       </c>
       <c r="C2" s="0">
-        <v>44407050</v>
+        <v>17872302419</v>
       </c>
       <c r="D2" s="0">
-        <v>444071</v>
+        <v>372961</v>
       </c>
       <c r="E2" s="0">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="F2" s="0">
-        <v>334</v>
+        <v>197500</v>
       </c>
       <c r="G2" s="0">
-        <v>3.3399999999999999</v>
+        <v>4.1200000000000001</v>
       </c>
       <c r="H2" s="0">
-        <v>8.5899999999999999</v>
+        <v>8.7300000000000004</v>
       </c>
       <c r="I2" s="0">
-        <v>82.989999999999995</v>
+        <v>81.640000000000001</v>
       </c>
       <c r="J2" s="0">
-        <v>886</v>
+        <v>707</v>
       </c>
       <c r="K2" s="0">
-        <v>6744</v>
+        <v>4696.5699999999997</v>
       </c>
       <c r="L2" s="0">
-        <v>44.960000000000001</v>
+        <v>36.689999999999998</v>
       </c>
       <c r="M2" s="0">
-        <v>0.13</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="3">
@@ -232,40 +235,40 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>12617785575</v>
+        <v>5926283365</v>
       </c>
       <c r="C3" s="0">
-        <v>14559053844</v>
+        <v>7156626956</v>
       </c>
       <c r="D3" s="0">
-        <v>441719</v>
+        <v>415118</v>
       </c>
       <c r="E3" s="0">
-        <v>183</v>
+        <v>150</v>
       </c>
       <c r="F3" s="0">
-        <v>86294</v>
+        <v>72187</v>
       </c>
       <c r="G3" s="0">
-        <v>2.6200000000000001</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="H3" s="0">
-        <v>6.4000000000000004</v>
+        <v>8.3800000000000008</v>
       </c>
       <c r="I3" s="0">
-        <v>86.670000000000002</v>
+        <v>82.810000000000002</v>
       </c>
       <c r="J3" s="0">
-        <v>921</v>
+        <v>661</v>
       </c>
       <c r="K3" s="0">
-        <v>5384</v>
+        <v>5196.1899999999996</v>
       </c>
       <c r="L3" s="0">
-        <v>29.379999999999999</v>
+        <v>34.640000000000001</v>
       </c>
       <c r="M3" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.105</v>
       </c>
     </row>
     <row r="4">
@@ -273,40 +276,40 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>5926283365</v>
+        <v>47736976660</v>
       </c>
       <c r="C4" s="0">
-        <v>7156626956</v>
+        <v>56016269515</v>
       </c>
       <c r="D4" s="0">
-        <v>415118</v>
+        <v>707008</v>
       </c>
       <c r="E4" s="0">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="F4" s="0">
-        <v>72187</v>
+        <v>289052</v>
       </c>
       <c r="G4" s="0">
-        <v>4.1900000000000004</v>
+        <v>3.6499999999999999</v>
       </c>
       <c r="H4" s="0">
-        <v>8.3800000000000008</v>
+        <v>10.35</v>
       </c>
       <c r="I4" s="0">
-        <v>82.810000000000002</v>
+        <v>85.219999999999999</v>
       </c>
       <c r="J4" s="0">
-        <v>661</v>
+        <v>1068</v>
       </c>
       <c r="K4" s="0">
-        <v>5196</v>
+        <v>6658.2700000000004</v>
       </c>
       <c r="L4" s="0">
-        <v>34.640000000000001</v>
+        <v>36.460000000000001</v>
       </c>
       <c r="M4" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="5">
@@ -314,40 +317,40 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>55692</v>
+        <v>22985146169</v>
       </c>
       <c r="C5" s="0">
-        <v>83538</v>
+        <v>26686540435</v>
       </c>
       <c r="D5" s="0">
-        <v>65535</v>
+        <v>1041223</v>
       </c>
       <c r="E5" s="0">
-        <v>126</v>
+        <v>196</v>
       </c>
       <c r="F5" s="0">
-        <v>1</v>
+        <v>77596</v>
       </c>
       <c r="G5" s="0">
-        <v>65535</v>
+        <v>3.0299999999999998</v>
       </c>
       <c r="H5" s="0">
-        <v>65535</v>
+        <v>12.539999999999999</v>
       </c>
       <c r="I5" s="0">
-        <v>66.670000000000002</v>
+        <v>86.129999999999995</v>
       </c>
       <c r="J5" s="0">
-        <v>663</v>
+        <v>1755</v>
       </c>
       <c r="K5" s="0">
-        <v>0</v>
+        <v>7151.8299999999999</v>
       </c>
       <c r="L5" s="0">
-        <v>0</v>
+        <v>36.490000000000002</v>
       </c>
       <c r="M5" s="0">
-        <v>0</v>
+        <v>0.085999999999999993</v>
       </c>
     </row>
     <row r="6">
@@ -355,40 +358,40 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>9408306321</v>
+        <v>51118535917</v>
       </c>
       <c r="C6" s="0">
-        <v>11275677997</v>
+        <v>60469391027</v>
       </c>
       <c r="D6" s="0">
-        <v>516759</v>
+        <v>549872</v>
       </c>
       <c r="E6" s="0">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="F6" s="0">
-        <v>88906</v>
+        <v>388487</v>
       </c>
       <c r="G6" s="0">
-        <v>4.0700000000000003</v>
+        <v>3.5299999999999998</v>
       </c>
       <c r="H6" s="0">
-        <v>9.1699999999999999</v>
+        <v>8.9800000000000004</v>
       </c>
       <c r="I6" s="0">
-        <v>83.439999999999998</v>
+        <v>84.540000000000006</v>
       </c>
       <c r="J6" s="0">
-        <v>808</v>
+        <v>905</v>
       </c>
       <c r="K6" s="0">
-        <v>5802</v>
+        <v>5872.4499999999998</v>
       </c>
       <c r="L6" s="0">
-        <v>36.960000000000001</v>
+        <v>34.140000000000001</v>
       </c>
       <c r="M6" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.096000000000000002</v>
       </c>
     </row>
     <row r="7">
@@ -396,40 +399,40 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>1922063505</v>
+        <v>10614785910</v>
       </c>
       <c r="C7" s="0">
-        <v>2314939632</v>
+        <v>12214778668</v>
       </c>
       <c r="D7" s="0">
-        <v>723419</v>
+        <v>694022</v>
       </c>
       <c r="E7" s="0">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="F7" s="0">
-        <v>13033</v>
+        <v>57103</v>
       </c>
       <c r="G7" s="0">
-        <v>4.0700000000000003</v>
+        <v>3.2400000000000002</v>
       </c>
       <c r="H7" s="0">
-        <v>10.949999999999999</v>
+        <v>10.42</v>
       </c>
       <c r="I7" s="0">
-        <v>83.030000000000001</v>
+        <v>86.900000000000006</v>
       </c>
       <c r="J7" s="0">
-        <v>971</v>
+        <v>1244</v>
       </c>
       <c r="K7" s="0">
-        <v>4533</v>
+        <v>5894.3500000000004</v>
       </c>
       <c r="L7" s="0">
-        <v>24.789999999999999</v>
+        <v>34.270000000000003</v>
       </c>
       <c r="M7" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.088999999999999996</v>
       </c>
     </row>
     <row r="8">
@@ -437,40 +440,40 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>25603554291</v>
+        <v>15532595384</v>
       </c>
       <c r="C8" s="0">
-        <v>31285656291</v>
+        <v>18351939793</v>
       </c>
       <c r="D8" s="0">
-        <v>660871</v>
+        <v>1410603</v>
       </c>
       <c r="E8" s="0">
-        <v>161</v>
+        <v>234</v>
       </c>
       <c r="F8" s="0">
-        <v>167954</v>
+        <v>19249</v>
       </c>
       <c r="G8" s="0">
-        <v>3.5499999999999998</v>
+        <v>1.48</v>
       </c>
       <c r="H8" s="0">
-        <v>10.859999999999999</v>
+        <v>12.119999999999999</v>
       </c>
       <c r="I8" s="0">
-        <v>81.840000000000003</v>
+        <v>84.640000000000001</v>
       </c>
       <c r="J8" s="0">
-        <v>1156</v>
+        <v>4078</v>
       </c>
       <c r="K8" s="0">
-        <v>5846</v>
+        <v>11341.780000000001</v>
       </c>
       <c r="L8" s="0">
-        <v>36.289999999999999</v>
+        <v>48.509999999999998</v>
       </c>
       <c r="M8" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.097000000000000003</v>
       </c>
     </row>
     <row r="9">
@@ -478,40 +481,40 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>14333342705</v>
+        <v>11733266488</v>
       </c>
       <c r="C9" s="0">
-        <v>17645316234</v>
+        <v>14020577519</v>
       </c>
       <c r="D9" s="0">
-        <v>743587</v>
+        <v>1743853</v>
       </c>
       <c r="E9" s="0">
-        <v>182</v>
+        <v>285</v>
       </c>
       <c r="F9" s="0">
-        <v>99124</v>
+        <v>11676</v>
       </c>
       <c r="G9" s="0">
-        <v>4.1799999999999997</v>
+        <v>1.45</v>
       </c>
       <c r="H9" s="0">
-        <v>11.029999999999999</v>
+        <v>12.300000000000001</v>
       </c>
       <c r="I9" s="0">
-        <v>81.230000000000004</v>
+        <v>83.689999999999998</v>
       </c>
       <c r="J9" s="0">
-        <v>978</v>
+        <v>4217</v>
       </c>
       <c r="K9" s="0">
-        <v>4719</v>
+        <v>13261.84</v>
       </c>
       <c r="L9" s="0">
-        <v>25.93</v>
+        <v>46.57</v>
       </c>
       <c r="M9" s="0">
-        <v>0.070000000000000007</v>
+        <v>0.094</v>
       </c>
     </row>
     <row r="10">
@@ -519,40 +522,40 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>13415427179</v>
+        <v>19282406437</v>
       </c>
       <c r="C10" s="0">
-        <v>16022492850</v>
+        <v>24007109278</v>
       </c>
       <c r="D10" s="0">
-        <v>459229</v>
+        <v>1399831</v>
       </c>
       <c r="E10" s="0">
-        <v>150</v>
+        <v>272</v>
       </c>
       <c r="F10" s="0">
-        <v>116067</v>
+        <v>23065</v>
       </c>
       <c r="G10" s="0">
-        <v>3.3300000000000001</v>
+        <v>1.3400000000000001</v>
       </c>
       <c r="H10" s="0">
-        <v>8.5</v>
+        <v>10.619999999999999</v>
       </c>
       <c r="I10" s="0">
-        <v>83.730000000000004</v>
+        <v>80.319999999999993</v>
       </c>
       <c r="J10" s="0">
-        <v>920</v>
+        <v>3828</v>
       </c>
       <c r="K10" s="0">
-        <v>5878</v>
+        <v>13951.860000000001</v>
       </c>
       <c r="L10" s="0">
-        <v>39.189999999999998</v>
+        <v>51.299999999999997</v>
       </c>
       <c r="M10" s="0">
-        <v>0.11</v>
+        <v>0.106</v>
       </c>
     </row>
     <row r="11">
@@ -560,40 +563,81 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>83263671726</v>
+        <v>10153289044</v>
       </c>
       <c r="C11" s="0">
-        <v>100304254392</v>
+        <v>13004998517</v>
       </c>
       <c r="D11" s="0">
-        <v>553311</v>
+        <v>1788858</v>
       </c>
       <c r="E11" s="0">
-        <v>164</v>
+        <v>304</v>
       </c>
       <c r="F11" s="0">
-        <v>643900</v>
+        <v>8830</v>
       </c>
       <c r="G11" s="0">
-        <v>3.5499999999999998</v>
+        <v>1.21</v>
       </c>
       <c r="H11" s="0">
-        <v>9.1699999999999999</v>
+        <v>11.93</v>
       </c>
       <c r="I11" s="0">
-        <v>83.010000000000005</v>
+        <v>78.069999999999993</v>
       </c>
       <c r="J11" s="0">
-        <v>947</v>
+        <v>4845</v>
       </c>
       <c r="K11" s="0">
-        <v>5527</v>
+        <v>16096.209999999999</v>
       </c>
       <c r="L11" s="0">
-        <v>33.659999999999997</v>
+        <v>52.950000000000003</v>
       </c>
       <c r="M11" s="0">
-        <v>0.089999999999999997</v>
+        <v>0.107</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0">
+        <v>209674168843</v>
+      </c>
+      <c r="C12" s="0">
+        <v>249800534127</v>
+      </c>
+      <c r="D12" s="0">
+        <v>728154</v>
+      </c>
+      <c r="E12" s="0">
+        <v>174</v>
+      </c>
+      <c r="F12" s="0">
+        <v>1144745</v>
+      </c>
+      <c r="G12" s="0">
+        <v>3.3399999999999999</v>
+      </c>
+      <c r="H12" s="0">
+        <v>9.9100000000000001</v>
+      </c>
+      <c r="I12" s="0">
+        <v>83.939999999999998</v>
+      </c>
+      <c r="J12" s="0">
+        <v>1147</v>
+      </c>
+      <c r="K12" s="0">
+        <v>7172.7200000000003</v>
+      </c>
+      <c r="L12" s="0">
+        <v>38.700000000000003</v>
+      </c>
+      <c r="M12" s="0">
+        <v>0.098000000000000004</v>
       </c>
     </row>
   </sheetData>
